--- a/InputData/plcy-schd/IT/Initial Time.xlsx
+++ b/InputData/plcy-schd/IT/Initial Time.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff-nonadmin\CodeRepositories\eps-us\InputData\plcy-schd\IT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\plcy-schd\IT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3B15C6-0640-4897-AB43-455C2238DA8D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC6B9E6-8492-47B5-AB74-054F3998C509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1320" windowWidth="24765" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -127,13 +127,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,7 +498,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
@@ -588,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
   </sheetData>
